--- a/cet4/result/22_重生钢琴_音乐才女的逆袭/22_重生钢琴_音乐才女的逆袭_学习版.xlsx
+++ b/cet4/result/22_重生钢琴_音乐才女的逆袭/22_重生钢琴_音乐才女的逆袭_学习版.xlsx
@@ -397,703 +397,605 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D42"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>eye</v>
       </c>
       <c r="B2" t="str">
-        <v>eye</v>
+        <v>/aɪ/</v>
       </c>
       <c r="C2" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D2" t="str">
         <v>眼睛</v>
       </c>
-      <c r="D2" t="str">
-        <v>eye(眼睛)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>weekly</v>
       </c>
       <c r="B3" t="str">
-        <v>weekly</v>
+        <v>/ˈwiːkli/</v>
       </c>
       <c r="C3" t="str">
+        <v>n./v./adj./adv.</v>
+      </c>
+      <c r="D3" t="str">
         <v>每周的</v>
       </c>
-      <c r="D3" t="str">
-        <v>weekly(每周的)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>haircut</v>
       </c>
       <c r="B4" t="str">
-        <v>haircut</v>
+        <v>/ˈherkʌt/</v>
       </c>
       <c r="C4" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D4" t="str">
         <v>理发</v>
       </c>
-      <c r="D4" t="str">
-        <v>haircut(理发)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>visible</v>
       </c>
       <c r="B5" t="str">
-        <v>visible</v>
+        <v>/ˈvɪzəbl/</v>
       </c>
       <c r="C5" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D5" t="str">
         <v>看得见的</v>
       </c>
-      <c r="D5" t="str">
-        <v>visible(看得见的)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>dormitory</v>
       </c>
       <c r="B6" t="str">
-        <v>dormitory</v>
+        <v>/ˈdɔːrmətɔːri/</v>
       </c>
       <c r="C6" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D6" t="str">
         <v>宿舍</v>
       </c>
-      <c r="D6" t="str">
-        <v>dormitory(宿舍)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>clean</v>
       </c>
       <c r="B7" t="str">
-        <v>clean</v>
+        <v>/kliːn/</v>
       </c>
       <c r="C7" t="str">
+        <v>n./vt./vi./v./adj./adv.</v>
+      </c>
+      <c r="D7" t="str">
         <v>干净</v>
       </c>
-      <c r="D7" t="str">
-        <v>clean(干净)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>England</v>
       </c>
       <c r="B8" t="str">
-        <v>England</v>
+        <v>/ˈɪŋɡlənd/</v>
       </c>
       <c r="C8" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D8" t="str">
         <v>英格兰</v>
       </c>
-      <c r="D8" t="str">
-        <v>England(英格兰)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>glad</v>
       </c>
       <c r="B9" t="str">
-        <v>glad</v>
+        <v>/ɡlæd/</v>
       </c>
       <c r="C9" t="str">
+        <v>n./vt./adj.</v>
+      </c>
+      <c r="D9" t="str">
         <v>高兴的</v>
       </c>
-      <c r="D9" t="str">
-        <v>glad(高兴的)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>primary</v>
       </c>
       <c r="B10" t="str">
-        <v>primary</v>
+        <v>/ˈpraɪmeri/</v>
       </c>
       <c r="C10" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D10" t="str">
         <v>初级的</v>
       </c>
-      <c r="D10" t="str">
-        <v>primary(初级的)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>garage</v>
       </c>
       <c r="B11" t="str">
-        <v>garage</v>
+        <v>/ˈɡærɑːʒ/</v>
       </c>
       <c r="C11" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D11" t="str">
         <v>车库</v>
       </c>
-      <c r="D11" t="str">
-        <v>garage(车库)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>together</v>
       </c>
       <c r="B12" t="str">
-        <v>together</v>
+        <v>/təˈɡeðər/</v>
       </c>
       <c r="C12" t="str">
+        <v>v./adj./adv.</v>
+      </c>
+      <c r="D12" t="str">
         <v>一起</v>
       </c>
-      <c r="D12" t="str">
-        <v>together(一起)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>feature</v>
       </c>
       <c r="B13" t="str">
-        <v>feature</v>
+        <v>/ˈfiːtʃər/</v>
       </c>
       <c r="C13" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D13" t="str">
         <v>特色</v>
       </c>
-      <c r="D13" t="str">
-        <v>feature(特色)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>diverse</v>
       </c>
       <c r="B14" t="str">
-        <v>diverse</v>
+        <v>/daɪˈvɜːrs/</v>
       </c>
       <c r="C14" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D14" t="str">
         <v>多样的</v>
       </c>
-      <c r="D14" t="str">
-        <v>diverse(多样的)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>Japanese</v>
       </c>
       <c r="B15" t="str">
-        <v>Japanese</v>
+        <v>/ˌdʒæpəˈniːz/</v>
       </c>
       <c r="C15" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D15" t="str">
         <v>日本的</v>
       </c>
-      <c r="D15" t="str">
-        <v>Japanese(日本的)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>Soviet</v>
       </c>
       <c r="B16" t="str">
-        <v>Soviet</v>
+        <v>/,sovɪ'et/</v>
       </c>
       <c r="C16" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D16" t="str">
         <v>苏联</v>
       </c>
-      <c r="D16" t="str">
-        <v>Soviet(苏联)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>moreover</v>
       </c>
       <c r="B17" t="str">
-        <v>moreover</v>
+        <v>/mɔːrˈoʊvər/</v>
       </c>
       <c r="C17" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D17" t="str">
         <v>而且</v>
       </c>
-      <c r="D17" t="str">
-        <v>moreover(而且)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>young</v>
       </c>
       <c r="B18" t="str">
-        <v>young</v>
+        <v>/jʌŋ/</v>
       </c>
       <c r="C18" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D18" t="str">
         <v>年轻的</v>
       </c>
-      <c r="D18" t="str">
-        <v>young(年轻的)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>warm</v>
       </c>
       <c r="B19" t="str">
-        <v>warm</v>
+        <v>/wɔːrm/</v>
       </c>
       <c r="C19" t="str">
+        <v>n./vt./vi./adj.</v>
+      </c>
+      <c r="D19" t="str">
         <v>温暖</v>
       </c>
-      <c r="D19" t="str">
-        <v>warm(温暖)📢</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>select</v>
       </c>
       <c r="B20" t="str">
-        <v>select</v>
+        <v>/sɪˈlekt/</v>
       </c>
       <c r="C20" t="str">
+        <v>vt./adj.</v>
+      </c>
+      <c r="D20" t="str">
         <v>选择</v>
       </c>
-      <c r="D20" t="str">
-        <v>select(选择)📢</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>radiate</v>
       </c>
       <c r="B21" t="str">
-        <v>radiate</v>
+        <v>/ˈreɪdieɪt/</v>
       </c>
       <c r="C21" t="str">
+        <v>vt./vi./adj.</v>
+      </c>
+      <c r="D21" t="str">
         <v>辐射</v>
       </c>
-      <c r="D21" t="str">
-        <v>radiate(辐射)📢</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>goodbye</v>
       </c>
       <c r="B22" t="str">
-        <v>goodbye</v>
+        <v>/ˌɡʊdˈbaɪ/</v>
       </c>
       <c r="C22" t="str">
+        <v>int.</v>
+      </c>
+      <c r="D22" t="str">
         <v>再见</v>
       </c>
-      <c r="D22" t="str">
-        <v>goodbye(再见)📢</v>
-      </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>occasionally</v>
       </c>
       <c r="B23" t="str">
-        <v>occasionally</v>
+        <v>/əˈkeɪʒnəli/</v>
       </c>
       <c r="C23" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D23" t="str">
         <v>偶尔</v>
       </c>
-      <c r="D23" t="str">
-        <v>occasionally(偶尔)📢</v>
-      </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>opera</v>
       </c>
       <c r="B24" t="str">
-        <v>opera</v>
+        <v>/ˈɑːprə/</v>
       </c>
       <c r="C24" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D24" t="str">
         <v>歌剧</v>
       </c>
-      <c r="D24" t="str">
-        <v>opera(歌剧)📢</v>
-      </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>drama</v>
       </c>
       <c r="B25" t="str">
-        <v>drama</v>
+        <v>/ˈdrɑːmə/</v>
       </c>
       <c r="C25" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D25" t="str">
         <v>戏剧性</v>
       </c>
-      <c r="D25" t="str">
-        <v>drama(戏剧性)📢</v>
-      </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>please</v>
       </c>
       <c r="B26" t="str">
-        <v>young</v>
+        <v>/pliːz/</v>
       </c>
       <c r="C26" t="str">
-        <v>年轻的</v>
+        <v>vt./vi./int.</v>
       </c>
       <c r="D26" t="str">
-        <v>young(年轻的)📢</v>
+        <v>使高兴</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>earthquake</v>
       </c>
       <c r="B27" t="str">
-        <v>please</v>
+        <v>/ˈɜːrθkweɪk/</v>
       </c>
       <c r="C27" t="str">
-        <v>使高兴</v>
+        <v>n.</v>
       </c>
       <c r="D27" t="str">
-        <v>please(使高兴)📢</v>
+        <v>地震</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>distress</v>
       </c>
       <c r="B28" t="str">
-        <v>earthquake</v>
+        <v>/dɪˈstres/</v>
       </c>
       <c r="C28" t="str">
-        <v>地震</v>
+        <v>n./vt.</v>
       </c>
       <c r="D28" t="str">
-        <v>earthquake(地震)📢</v>
+        <v>悲痛</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>weep</v>
       </c>
       <c r="B29" t="str">
-        <v>distress</v>
+        <v>/wiːp/</v>
       </c>
       <c r="C29" t="str">
-        <v>悲痛</v>
+        <v>n./v.</v>
       </c>
       <c r="D29" t="str">
-        <v>distress(悲痛)📢</v>
+        <v>哭泣</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>outline</v>
       </c>
       <c r="B30" t="str">
-        <v>weep</v>
+        <v>/ˈaʊtlaɪn/</v>
       </c>
       <c r="C30" t="str">
-        <v>哭泣</v>
+        <v>n./vt.</v>
       </c>
       <c r="D30" t="str">
-        <v>weep(哭泣)📢</v>
+        <v>大纲</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>gently</v>
       </c>
       <c r="B31" t="str">
-        <v>outline</v>
+        <v>/ˈdʒentli/</v>
       </c>
       <c r="C31" t="str">
-        <v>大纲</v>
+        <v>v./adv.</v>
       </c>
       <c r="D31" t="str">
-        <v>outline(大纲)📢</v>
+        <v>温柔</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>abnormal</v>
       </c>
       <c r="B32" t="str">
-        <v>gently</v>
+        <v>/æbˈnɔːrml/</v>
       </c>
       <c r="C32" t="str">
-        <v>温柔</v>
+        <v>adj.</v>
       </c>
       <c r="D32" t="str">
-        <v>gently(温柔)📢</v>
+        <v>反常的</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>age</v>
       </c>
       <c r="B33" t="str">
-        <v>abnormal</v>
+        <v>/eɪdʒ/</v>
       </c>
       <c r="C33" t="str">
-        <v>反常的</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D33" t="str">
-        <v>abnormal(反常的)📢</v>
+        <v>年龄</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>ore</v>
       </c>
       <c r="B34" t="str">
-        <v>together</v>
+        <v>/ɔːr/</v>
       </c>
       <c r="C34" t="str">
-        <v>一起</v>
+        <v>n.</v>
       </c>
       <c r="D34" t="str">
-        <v>together(一起)📢</v>
+        <v>矿石</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>audience</v>
       </c>
       <c r="B35" t="str">
-        <v>age</v>
+        <v>/ˈɔːdiəns/</v>
       </c>
       <c r="C35" t="str">
-        <v>年龄</v>
+        <v>n.</v>
       </c>
       <c r="D35" t="str">
-        <v>age(年龄)📢</v>
+        <v>观众</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>recommendation</v>
       </c>
       <c r="B36" t="str">
-        <v>ore</v>
+        <v>/ˌrekəmenˈdeɪʃn/</v>
       </c>
       <c r="C36" t="str">
-        <v>矿石</v>
+        <v>n.</v>
       </c>
       <c r="D36" t="str">
-        <v>ore(矿石)📢</v>
+        <v>推荐</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>imagination</v>
       </c>
       <c r="B37" t="str">
-        <v>audience</v>
+        <v>/ɪˌmædʒɪˈneɪʃn/</v>
       </c>
       <c r="C37" t="str">
-        <v>观众</v>
+        <v>n.</v>
       </c>
       <c r="D37" t="str">
-        <v>audience(观众)📢</v>
+        <v>想象力</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>data</v>
       </c>
       <c r="B38" t="str">
-        <v>radiate</v>
+        <v>/ˈdeɪtə,ˈdætə/</v>
       </c>
       <c r="C38" t="str">
-        <v>辐射</v>
+        <v>n.</v>
       </c>
       <c r="D38" t="str">
-        <v>radiate(辐射)📢</v>
+        <v>数据</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>repeat</v>
       </c>
       <c r="B39" t="str">
-        <v>recommendation</v>
+        <v>/rɪˈpiːt/</v>
       </c>
       <c r="C39" t="str">
-        <v>推荐</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D39" t="str">
-        <v>recommendation(推荐)📢</v>
+        <v>重复</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>probable</v>
       </c>
       <c r="B40" t="str">
-        <v>Japanese</v>
+        <v>/ˈprɑːbəbl/</v>
       </c>
       <c r="C40" t="str">
-        <v>日本的</v>
+        <v>n./adj.</v>
       </c>
       <c r="D40" t="str">
-        <v>Japanese(日本的)📢</v>
+        <v>可能的</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>prosperity</v>
       </c>
       <c r="B41" t="str">
-        <v>imagination</v>
+        <v>/prɑːˈsperəti/</v>
       </c>
       <c r="C41" t="str">
-        <v>想象力</v>
+        <v>n.</v>
       </c>
       <c r="D41" t="str">
-        <v>imagination(想象力)📢</v>
+        <v>繁荣</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>greet</v>
       </c>
       <c r="B42" t="str">
-        <v>data</v>
+        <v>/ɡriːt/</v>
       </c>
       <c r="C42" t="str">
-        <v>数据</v>
+        <v>n./vt.</v>
       </c>
       <c r="D42" t="str">
-        <v>data(数据)📢</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43">
-        <v>42</v>
-      </c>
-      <c r="B43" t="str">
-        <v>garage</v>
-      </c>
-      <c r="C43" t="str">
-        <v>车库</v>
-      </c>
-      <c r="D43" t="str">
-        <v>garage(车库)📢</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44">
-        <v>43</v>
-      </c>
-      <c r="B44" t="str">
-        <v>repeat</v>
-      </c>
-      <c r="C44" t="str">
-        <v>重复</v>
-      </c>
-      <c r="D44" t="str">
-        <v>repeat(重复)📢</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45">
-        <v>44</v>
-      </c>
-      <c r="B45" t="str">
-        <v>audience</v>
-      </c>
-      <c r="C45" t="str">
-        <v>观众</v>
-      </c>
-      <c r="D45" t="str">
-        <v>audience(观众)📢</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46">
-        <v>45</v>
-      </c>
-      <c r="B46" t="str">
-        <v>probable</v>
-      </c>
-      <c r="C46" t="str">
-        <v>可能的</v>
-      </c>
-      <c r="D46" t="str">
-        <v>probable(可能的)📢</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47">
-        <v>46</v>
-      </c>
-      <c r="B47" t="str">
-        <v>prosperity</v>
-      </c>
-      <c r="C47" t="str">
-        <v>繁荣</v>
-      </c>
-      <c r="D47" t="str">
-        <v>prosperity(繁荣)📢</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48">
-        <v>47</v>
-      </c>
-      <c r="B48" t="str">
-        <v>greet</v>
-      </c>
-      <c r="C48" t="str">
         <v>问候</v>
-      </c>
-      <c r="D48" t="str">
-        <v>greet(问候)📢</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49">
-        <v>48</v>
-      </c>
-      <c r="B49" t="str">
-        <v>together</v>
-      </c>
-      <c r="C49" t="str">
-        <v>一起</v>
-      </c>
-      <c r="D49" t="str">
-        <v>together(一起)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D49"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D42"/>
   </ignoredErrors>
 </worksheet>
 </file>